--- a/docs/AlphaAIConsultApS(Gennemgangafhovedkrav)Anmodningomoplysninger.xlsx
+++ b/docs/AlphaAIConsultApS(Gennemgangafhovedkrav)Anmodningomoplysninger.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="47.7109375" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>OIOUBL 2.1 (type 380) via Storecove/NemHandel.</t>
+          <t>OIOUBL 2.1 (type 380) via Sproom/NemHandel — raw XML POST /api/documents (Sproom Access Point).</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. OIOUBL 2.1 (type 380) afsendes via Storecove/NemHandel. Se Bilag 4 afsnit 2.1 og Bilag 6 afsnit 6.4. NemHandel demo-endepunkter for alle fire endepunkts-ID-typer vil blive fremsendt separat som bilag til denne anmodning (jf. https://nemhandel.dk/vejledning-til-nemhandel-demo-miljoe-test-miljoe).</t>
+          <t>Kravet er opfyldt. OIOUBL 2.1 (type 380) afsendes via Sproom (NemHandel + Peppol Access Point). Se Bilag 4 afsnit 2.1 og Bilag 6 afsnit 6.4. NemHandel demo-endepunkter for alle fire endepunkts-ID-typer vil blive fremsendt separat som bilag til denne anmodning (jf. https://nemhandel.dk/vejledning-til-nemhandel-demo-miljoe-test-miljoe).</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Kreditnota-oprettelsesflow er implementeret i UI (KRE-{år}-{seq}, spejlet bogføring), og OIOUBL-download-endpoint returnerer korrekt type 381. MEN einvoice-sender.ts hardcoder invoiceTypeCode='380' i buildOIOUBLData(), og queueEInvoiceSend henter ikke invoice.documentType — kreditnota sendes derfor som type 380 (almindelig faktura) i stedet for 381. Kreditnota kan ikke reelt afsendes som OIOUBL type 381.</t>
+          <t>Kreditnotaer afsendes som OIOUBL type 381: einvoice-sender.ts vælger invoiceTypeCode ud fra invoice.documentType === 'CREDIT_NOTE' (fallback creditNotePrefix 'KRE-'), og oioubl-generator.ts emitterer korrekt &lt;CreditNote&gt;-rodelement med cac:CreditNoteLine/cbc:CreditedQuantity og cac:BillingReference til originalfakturaen. Fuldt understøttet.</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Peppol BIS Billing 3.0 via Storecove Access Point.</t>
+          <t>Peppol BIS Billing 3.0 via Sproom Access Point (dansk AP — Peppol + NemHandel).</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Kravet er opfyldt. Peppol BIS Billing 3.0 afsendes via Storecove Access Point. Se Bilag 4 afsnit 2.1 og Bilag 6 afsnit 6.4. Standardiseret Peppol testbed-rapport vil blive fremsendt separat som bilag.</t>
+          <t>Kravet er opfyldt. Peppol BIS Billing 3.0 afsendes via Sproom Access Point. Se Bilag 4 afsnit 2.1 og Bilag 6 afsnit 6.4. Standardiseret Peppol testbed-rapport vil blive fremsendt separat som bilag.</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Samme begrænsning som OIOUBL kreditnota — oprettelsesflow er implementeret, men send-pipeline (einvoice-sender.ts) hardcoder type 380. Peppol BIS-afsendelse transmitterer derfor 380 i stedet for 381. Kreditnota kan ikke reelt afsendes som Peppol BIS kreditnota.</t>
+          <t>Kreditnotaer afsendes som Peppol BIS Billing 3.0 type 381 via Sproom — samme pipeline som OIOUBL (documentType CREDIT_NOTE vælger 381 med BillingReference). Fuldt understøttet.</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (bank) + Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (bankforbindelser) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 12 + Bilag 12 (Bilag-12_Udbedringsplan.md). Delvist: kun Tink + Demo reelle.</t>
+          <t>Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (bank) + Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (bankforbindelser) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 7 + Bilag 12 (Bilag-12_Udbedringsplan.md). Delvist: kun Tink + Demo reelle.</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (PSD2 consent-flow) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 12. Delvist: consent virker for Tink; stubs for øvrige banker.</t>
+          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 8.1 (PSD2 consent-flow) + Bilag 1 (Bilag-01_Anmeldelsespakke.md) afsnit 8 punkt 7. Delvist: consent virker for Tink; stubs for øvrige banker.</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Tilmelding via Storecove (Peppol/NemHandel Access Point).</t>
+          <t>Tilmelding via Sproom (Peppol/NemHandel Access Point) — child company pr. CVR oprettes automatisk og registreres i begge netværk.</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 16.3 + Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (Storecove som Access Point) + Bilag 12 (Bilag-12_Udbedringsplan.md) afsnit 6 (mangel 5 — NemHandel simulering ved manglende AP-aftale).</t>
+          <t>Bilag 6 (Bilag-06_Brugsvejledning.md) afsnit 16.3 + Bilag 4 (Bilag-04_Compliance-rapport.md) afsnit 2.1 (Sproom som Access Point) + Bilag 12 (Bilag-12_Udbedringsplan.md) U-9 (Sproom-aftale indgået — staging aktiv, produktion via env-switch).</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>KRAVET ER FULDT OPFYLDT. Tilmelding til NemHandelsregisteret håndteres via Storecove Access Point (src/lib/einvoice-sender.ts → registerNemHandel). Flow: (1) In-app banner / e-mail oplyser om muligheden; (2) kunden går til Indstillinger → e-faktura-indstillinger; (3) kunden markerer ønske om tilmelding og giver samtykke; (4) AlphaFlow håndterer tilmeldingen via Storecove (Peppol/NemHandel Access Point) ud fra gældende NemHandel-standarder. Se Bilag 6 afsnit 16.3 + 16.11 og Bilag 4 afsnit 2.1. Skærmbilleder vil blive fremsendt.</t>
+          <t>KRAVET ER FULDT OPFYLDT. Tilmelding til NemHandelsregisteret håndteres via Sproom Access Point (src/app/api/sproom/register-nemhandel → src/lib/sproom-client.ts). Flow: (1) In-app banner / e-mail oplyser om muligheden; (2) kunden går til Indstillinger → e-faktura-indstillinger; (3) kunden markerer ønske om tilmelding og giver samtykke; (4) AlphaFlow håndterer tilmeldingen via Sproom (Peppol/NemHandel Access Point — child company pr. CVR, registrering i begge netværk) ud fra gældende NemHandel-standarder. Se Bilag 6 afsnit 16.3 + 16.11 og Bilag 4 afsnit 2.1. Skærmbilleder vil blive fremsendt.</t>
         </is>
       </c>
     </row>
